--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jun-2025.xlsx
@@ -562,7 +562,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1667,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1732,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1797,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1923,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1988,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2053,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2118,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2313,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2343,7 +2439,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2404,7 +2504,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2569,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2695,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2760,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2709,7 +2825,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2770,7 +2890,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2896,7 +3020,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2957,7 +3085,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3083,7 +3215,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3144,7 +3280,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3205,7 +3345,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3266,7 +3410,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3327,7 +3475,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3388,7 +3540,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3449,7 +3605,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3510,7 +3670,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
